--- a/data/Replace_values.xlsx
+++ b/data/Replace_values.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="valeurs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2192,1778 +2191,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Renamed</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Regex_valide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:non|no|n|false|faux|0(?:\.0)?|n0n)\s*$</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:oui|yes|y|true|vrai|1(?:\.0)?)\s*$</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:eleve|?lev?|haut|high)\s*$</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>?lev?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Niveau_risque</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:faible|bas|low)\s*$</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Faible</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Niveau_risque</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:moyen|modere|mod?r?|medium)\s*$</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Moyen</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Niveau_risque</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:non\s+renseigne|non\s+renseign?|inconnu|nd|n/?a)\s*$</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Non renseign?</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Niveau_risque</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:agriculteur\(trice\)/cultivateur\(trice\)|agriculteur(?:s)?|agricultrice(?:s)?|agriculture|agriculteur\s*\(cultivateur\)\s*/?\s*horticulture|agriculteur/horticulture|agricultricece|c\s*ultivatrice|cultivateur|cultivatrice|cultivateur/trice|cultivat(?:eur|rice)?|cultivat\.?|cultiv\.?|cult\.?|cultrice|culticvatrice|cultiv|cultivatice|cultivatirice|cultivatrcice|cultivatriec|cultivatrise|cultivatrivce|cultivatr|cultivatri|cultivatruce|culitivatrice|culitvatrice|cultuvat|cultuvatreur|cultuvateur|cultuvatrce|cultuvatrice|cultivatteur|cultivztrice|cultivteur|cuktiv|culti|cultiveteyr|clt|cu|cul|ultiv|fermi(?:er|ere|ère)|paysan(?:t|te)?s?|exploitant(?:e)?(?:\s*agricole)?|horticulteur|mara[îi]ch(?:er|ere|ère)?s?|marechaire|jardinier(?:e)?s?|jardini[eè]re\s+de\s+tomates|eleveur|eleeveur|berger|bouvier|bascourier)\s*$</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Agriculteur(trice)/Cultivateur(trice)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:artisan|petits?\s+artisans?|menuis(?:i|ie)r(?:e)?s?|menusier|menuisier|menier|me?n[ui]er(?:e)?|menisien|menuicien|coutur(?:i|ie)er(?:e)?s?|coutiriere|couturie|couturieur|couturire|coutyriere|tailleur|tailleuse|coiff(?:eur|euse)s?|plombier(?:s)?|soud(?:e|eu)r(?:s)?|sudeur|m[ée]canic(?:ien|ienne|iene)|mecani(?:cien|ssien|cien(?:ne)?)s?|electricien(?:ne)?s?|peintre|pentre|photographe|photographie|boulanger|boulager|boucher|barman|cuisinier(?:e)?s?|restaurantrice|serveur|hotelier|charpentier|cordonnier|coordonnier|coordonnoier|reparateur|repateur|decorateur|ajusteur|ajuteur|esth[ée]tic(?:ien|ienne|iene)|fabricateur\s+des\s+braises|ferrailler|ferrailleur|grimen|grimier)\b.*$</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Artisan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:chauffeur/transport|chau?ff?eur(?:s)?|chauff|chofeur|chaufeur|chauffer|ch0ffeur\s+de\s+la\s+balegnere|aide\s*chauffeur|chauffeur/mecanicien|conducteur(?:s)?|conductrice(?:s)?|convoyeur(?:s)?|livreur(?:s)?|taxi\s*men|taxim(?:en|ene)?|transport|equipage|equipage\s*/\s*camion|capitaine|matel[oa]t|maitre\s*matelot|navigant|navigateur|tolekiste|pousse?pousseur|pouspouseur|porteur|chauffeur\s+de\s+bateau.*|motard|montard|moate|motocycliste|moto(?:c?ycliste|rd|tar?d|tar)|pedaleur|piroguier\s*taxis?|recepteur|receveur|gbodoliste)\b.*$</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chauffeur/Transport</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:commerçant\(e\)|commerçant€|commer[cç]ant(?:e)?s?|commeracant|commerciant|cmmercant|c0mmercant|comercant(?:e)?s?|comerce|comlerce|comercent|commerca|commercent|commercente|commerce|petit(?:e)?\s*commerce|petit\s*com|marchand/?e?|revendeur|ambulant|changeur\s+de\s+monnai?e?s?|chargeur|vendeu(?:r|se)|vendeur|vendeuse|vendueur|vendeuyse|vendeuse\s*poisson|vandeuse|nendeur|ven[dt]eu(?:r|se)s?(?:\s*(?:de|du|des)\s*.+)?|poissoniere|caissiere|trafic(?:ant|ante|at|quant)|trafiqu(?:ant|ante|quant|at)|trafiquent|trafiquente|tranficante|ind[ée]pendant(?:e)?|lib[ée]ral(?:e)?|armateur|business|bisnesert|busnese|d[ée]b(?:ou|ro?u)ill?ard|d[ée]bri(?:a)?ll?ard|debrieur|d[ée]bri?ard|d[ée]br[ui]ll?ant|d[ée]brouill?ant|d[ée]broull?ard|d[ée]mbrull?ent|d?embrullent|chasseur(?:\s*/\s*vendeur\s+de\s+viande\s+de\s+la\s+brousse)?|voyageur\s*/\s*commercant|commercant\s*/\s*voyageur)\b.*$</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Commerçant(e)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:enfant(?:s)?|fnfant|enf(?:ant[es]?)?|enfant\s+non\s+scolaris[ée]?|enfant\s+scolaris[ée]?|non\s+scolaris[ée]?|bb|b[ée]b[eé]s?|bbé|fillette|nourr?i?son|nourion|nourison|nourisson|nourrison|nouriisson|gd\s+nourion|petit\s*enf|petit\s*enfant|jeune\s+en\s+situation\s+de\s+rue|shegue)\b.*$</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Enfant</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:enseignant\(e\)/professeur|enseignant(?:e)?|enseignant\s*\(e\)|ensei(?:gnant|gnante|gent|gant|gnt|egnant|egnante)|enseingnant|ens[ei]e?g(?:n(?:ant(?:e)?|ent)|ant(?:e)?|nt|nt\s*\(e\))|ense{1,2}i?g?n?[ae]?n?t(?:e)?|prof|professeur|proffeseur|maitresse|ma[iî]tre|isn?pecteur/?ensei?gnant(?:e)?)\b.*$</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Enseignant(e)/Professeur</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:fonctionnaire|fonctionnairs|f0ncionnaire|foctionnaire|fonctonnaire|fonctionne(?:lle)?|fonctionnelke|ag(?:ent)?(?:\s+de)?\s+l[’']?\s*etat|ag\s+de\s+l[’']?\s*etat|agent\s+(?:mairie|dgi|dgrad|regideso|resideso|anr|environnement|a\s+la\s+banque|snel|ovd|sonas)|agens\s+snel|mairie|prefet|inspecteur|insperteur|isnpecteur|chef\s+(?:d[eéu]\s+quartier|avenue)|recen[cs]+eur(?:se)?|anr|o\s*v\s*d|sonas)\b.*$</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Fonctionnaire</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:humanitaire/ong|humanitaire(?:\s*wfp)?|ong|cooperant|cooperation|volontaire|animateur|animatrice)\b.*$</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Humanitaire/ONG</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:inconnu/non\s*renseigné|inconnu/non\s*renseigne|agent|non|non\s*connue|non\s*connu|na|n\s*a|n\.?a\.?|nd|n\.?d\.?|nan|vide|\(vide\)|aucune|autre|autres|s|sp|ps|pas|\?+|0|8|9|12|14|48|anaphabette|analphabete|contact|av\s*kapanda|boyoka|goma|karisimbi|kasulo|katoyi|kirotshe|manika\s*metho|musompo|nyiragongo|nord\s*kivu|gwado|carelaire|chariomene|chukudeur|kimalamungo|manite|rras|ee|diplome|dariste|joueur|jouer|footballeur|artiste|boxeur|bukena|kumbula|umana\s*port|chezlit|to\s*hgr|tl|dgrtang|reco|charmeur|charmeuse|charmeurse|perciv|ts|disseleur)?\s*$</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Inconnu/Non renseigné</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:justice/détention|justice/detention|prisonnier|detenu|detenue|détenu|détenue|greffier|avocat|juge)\b.*$</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Justice/Détention</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:management|manager|managere|manageur|g[ée]rant(?:e)?|direct(?:eur|rice)|chef\s+de\s*service|secr[ée]taire|administratif|cabinet)\b.*$</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:militaire/police|militaire|militaires|millitaire|mitaire|militeur|milit(?:aire|eur)|f\.?\s*militaire|femme\s+militaire|soldat(?:s)?|fardc|commandant\s*fn|police|poliice|polici(?:er|ere|en)?s?|polic[iy]e?|policie|policien|garde|garde\s+parc|gardien(?:s)?(?:\s+de\s+maison)?|sentinelle|sentinel|sentin(?:elle|el|el?e)?|sentile|securite|ecurite|securyte|securyti|pompier)\b.*$</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Militaire/Police</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:mine/extraction|mineur|division\s*mine|creuseur|creuser|cres(?:se)?ur|cresuer|creseur|cresueur|creuseur\s+d['’\s]?or|cre?seur\s+d['’\s]?or|minier|concasseur|sablonier|sablonnier|rocher|agent\s+kcc|kcc|somika|t\s*f\s*m|tfm)\b.*$</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mine/Extraction</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:m[ée]nag[èe]re?|menag(?:eur|ere|er|ere?s)?|menage|menageure|menageur|menanger|menangeur|menegere|menangere|megere|manege|menageree|menagre|menareur|mene|mengeur|femme(?:s)?\s+au\s+foyer|travail\s+domestique|domestique|bonne|manegere)\b.*$</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ménagère</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:ouvrier/btp/logistique|ouvrier|ouvri(?:er|e)?:?(?:\s*qualifi[ée]?)?|docker|docke?ur(?:euse)?|dockeur|macon|maçon|mason|man\w*con|brquitier|briquetier|planchier|magasinier|magasignier|magasini?er(?:e)?|d[ée]bard(?:eur|euse)?|debard|manutention(?:naire)?|manu?tention|machiniste|machinistre|frigoriste|nettoyeur\s+de\s+vehicule|netoyeur\s+de\s+vehicule|travailleur|travaille|travailleur\s+de\s+megaplast|tout\s*trava[ui]l|tout\s*trav(?:ail|aux)|tout\s*t[ée]rain|tou[st]\s*trav(?:e?a)?ux(?:\s*divers)?|tou[st]\s*trava(?:il|ux)\s*(?:divers)?|trav(?:e?a)?ux\s*tou[st]|travaux\s*divers|tt\s*trav(?:e?a)?ux|graisseur|gresseur|emplo[yi][eé]s?|emplo[yi]é?e?|employ[ée]e?|recen[cs]seur|operateur|usine|agent\s+brasimba|brasimba|grumier)\b.*$</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ouvrier/BTP/Logistique</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:professionnel\s+de\s+sexe|professionnelle\s+de\s+sexe|prof\s*sexe|personne\s+de\s+sexe|danseuse)\b.*$</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Professionnel de sexe</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:pêcheur|pecheur|p[ée]cheu?r?|pe\s*cheur(?:e)?s?|pecheu\s*r|pecheu|peceur|peucheur|pecheuse|pecheur/motard|pecheurs?)\b.*$</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Pêcheur</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:religion|pasteur|pateur|pr[ée]tre|p[eè]re|imam|[ée]vang[ée]liste|evangeliste|religieu(?:se)?|choriste)\b.*$</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Religion</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:retrait[ée]?|retraite)\b.*$</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Retraité</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:sans\s*emploi|sans|sans\s+profe?ssion|sans\s+travail|sans\s+fonction|sans\s*occ|sansocc|s-prof|sans\s*frofession|ch[oô]meur|ch[oô]meuse|chaumeur|chaumer|sans\s*p|sinistre|veuf|veuve|rod[ée]ur(?:se)?|dep(?:lac[ée]?|arat))\b.*$</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Sans emploi</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:santé|sante|agent\s+de\s+sante|per\s+de\s+sante|pro\s+sante|prosante|ppl|personnel\s+soignant|medecin(?:s)?|i?m?firmier(?:e)?s?|infimier|infirmi(?:e|è)re?s?|infirmier|infirmière|aide\s+infirmier|sage\s*femme|femme\s+sage|matrone(?:s)?|pharmacien(?:ne)?s?|pr[ée]pos[ée]e?\s*(?:à|a)\s*la\s*pharmacie|t(?:c|e)hnicien(?:\s+de)?\s+labo|tchnicien\s+de\s+labo|hygieniste|secouriste|accouchese|soignat|soignant|tradipraticien(?:ne)?|tradi\.\s*praticien|tradi\s*praticien)\b.*$</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Santé</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:technique/ingénierie|technique/ingenierie|informaticien(?:ne)?s?|ing[ée]nieur(?:e|s)?|ingenieur(?:e|s)?|injenier|technicien(?:ne)?s?(?!.*labo)|technitient|techicien|tech\s+de\s+surface|tech|t[ée]l[ée]com|telecom|manager\s+informatique|environnementalogue|agist?eur|c\.?t\s*a\s*l['’]?ista)\b.*$</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Technique/Ingénierie</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:voyageur|voyageuse|voyagaire|voyagere|vacancier)\b.*$</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Voyageur</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:[ée]l[èe]ve|élève|eleve|elebe|eleve/pecheur|ecolier(?:e)?s?|ecoliier|ecolierr|e[ée]l[èe]ve?|e+[lv]e|elve|eeve|leve|etudian?t(?:e)?s?|étudiant|étudiante|etudant|etudiante|etudianye|edudiant|eetudiant|eetudiante|etudient|etudiente|en\s+scolarite|en\s+scolaris[ée]?|pre\s*scolaire|maternelle)\b.*$</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Élève/Étudiant</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Profession</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>(?i)^\s*bas[\s_-]*uele\s*$</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Bas Uele</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>(?i)^\s*equateur\s*$</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Equateur</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>(?i)^\s*haut[\s_-]*katanga\s*$</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Haut Katanga</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>(?i)^\s*haut[\s_-]*lomami\s*$</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Haut Lomami</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>(?i)^\s*haut[\s_-]*uele\s*$</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Haut Uele</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>(?i)^\s*ituri\s*$</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Ituri</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kasai\s*$</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Kasai</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kasai[\s_-]*central\s*$</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Kasai Central</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kasai[\s_-]*oriental\s*$</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Kasai Oriental</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kinshasa\s*$</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Kinshasa</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kongo[\s_-]*central\s*$</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Kongo Central</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kwango\s*$</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Kwango</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>(?i)^\s*kwilu\s*$</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Kwilu</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>(?i)^\s*lomami\s*$</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Lomami</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>(?i)^\s*lualaba\s*$</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Lualaba</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>(?i)^\s*ma[iï]\s*[-\s]*ndombe\s*$</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Maindombe</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>(?i)^\s*maniema\s*$</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Maniema</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>(?i)^\s*mongala\s*$</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Mongala</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>(?i)^\s*nord[\s_-]*kivu\s*$</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Nord Kivu</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>(?i)^\s*nord[\s_-]*ubangi\s*$</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nord Ubangi</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>(?i)^\s*sankuru\s*$</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sankuru</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>(?i)^\s*sud[\s_-]*kivu\s*$</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sud Kivu</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>(?i)^\s*sud[\s_-]*ubangi\s*$</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sud Ubangi</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>(?i)^\s*tanganyika\s*$</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Tanganyika</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>(?i)^\s*tshopo\s*$</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Tshopo</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>(?i)^\s*tshuapa\s*$</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Tshuapa</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:1|1\.0|1,0|f|ff|fem|femme|feminin|féminin|f[ée]minin|female)\s*$</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Féminin</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Sexe</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:9|9\.0|9,0|99|999|inconnu|indetermine|indéterminé|unknown|unk|nd|n/a|na|null|nan|vide)\s*$</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Sexe</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>^\s*$</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Sexe</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:2|2\.0|2,0|m|mm|masc|masculin|male|hom|homme|h|hh|garcon|garçon|g)\s*$</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Masculin</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Sexe</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:a\s+completer|?\s+completer|a\s+compl[?e]ter|?\s+compl[?e]ter|incomplet|dossier\s+incomplet)\s*$</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>? compl?ter</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:approuve|approuv?|accorde|accord?|valide|valid?)\s*$</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Approuv?</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:cloture|cl?tur?|clotur?|clos)\s*$</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Cl?tur?</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:decaisse|d?caiss?|decaiss?|decaissement\s+effectif)\s*$</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>D?caiss?</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:en\s+analyse|en\s+cours|analyse\s+en\s+cours)\s*$</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>En analyse</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:en\s+remboursement|remboursement\s+en\s+cours)\s*$</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>En remboursement</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:en\s+retard|retard)\s*$</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>En retard</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:recu|re?u|dossier\s+recu|dossier\s+re?u)\s*$</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Re?u</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:rejete|rejet?|refuse|refus?)\s*$</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Rejet?</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Statut_dossier</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:a\s+jour|?\s+jour|normal|regulier|r?gulier)\s*$</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>? jour</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Statut_remboursement</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:en\s+retard|impaye|impay?|retard|arrears?)\s*$</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>En retard</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Statut_remboursement</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:non\s+decaisse|non\s+d?caiss?|non\s+decaiss?|pas\s+decaisse|pas\s+d?caiss?)\s*$</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Non d?caiss?</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Statut_remboursement</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:solde|sold?|cloture|cl?tur?|clotur?|rembourse)\s*$</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Sold?</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Statut_remboursement</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:personne\s+morale|societe|soci?t?|entreprise|pm)\s*$</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Personne morale</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Type_client</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:personne\s+physique|client\s+individuel|individuel|pp)\s*$</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Personne physique</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Type_client</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:&lt;na&gt;|nan|none|null|nd|n\.?d\.?|inconnu|vide|\(vide\)|\?+)?\s*$</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Unite_age</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:jour|jours|j)\s*$</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Jours</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Unite_age</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:an|ans|année|annee|ann[ée]es?|a)\s*$</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ans</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Unite_age</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>(?i)^\s*(?:mois|moi|m)\s*$</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>mois</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Unite_age</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>VRAI</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/Replace_values.xlsx
+++ b/data/Replace_values.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2188,6 +2188,1304 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>(?i)^\s*038_SYNTHESE_HISTORIQUE_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>38 - Synthèse historique LBC-FT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>(?i)^\s*039_FRACTIONNEMENT_POTENTIEL\s*$</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>39 - Fractionnement potentiel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>(?i)^\s*048_TROUS_COUVERTURE_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>48 - Couverture du dispositif LBC-FT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>(?i)^\s*057_GROS_MOUVEMENTS_PERIODE\s*$</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>57 - Gros mouvements par période</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149_REPORTING_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>149 - Reporting LBC-FT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149_DETAIL_MOUVEMENTS_REPORTING_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>149 - Détail des mouvements du reporting</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149_DETAIL_REMBOURSEMENTS_ANTICIPES\s*$</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>149 - Remboursements anticipés</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>(?i)^\s*150_ALERTES_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>150 - Alertes LBC-FT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>(?i)^\s*151_DECLARATIONS_SOUPCON_CENTIF\s*$</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>151 - Déclarations de soupçon CENTIF</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>(?i)^\s*152_PROFILS_RISQUE_CLIENTS\s*$</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>152 - Profils de risque clients</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>(?i)^\s*153_REFERENTIEL_SANCTIONS\s*$</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>153 - Référentiel sanctions</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>(?i)^\s*154_COMPTES_DORMANTS_REACTIVES\s*$</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>154 - Comptes dormants réactivés</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>(?i)^\s*155_QUALITE_DONNEES_LBC_FT\s*$</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>155 - Qualité des données LBC-FT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>(?i)^\s*REPORTING\s*$</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Reporting agrégé</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>(?i)^\s*MOUVEMENT_OPERATION\s*$</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mouvement</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>(?i)^\s*REMBOURSEMENT_ANTICIPE\s*$</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Remboursement anticipé</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>(?i)^\s*ALERTE\s*$</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Alerte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>(?i)^\s*DECLARATION\s*$</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Déclaration</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>(?i)^\s*PROFIL_RISQUE\s*$</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Profil de risque</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>(?i)^\s*BLACKLIST\s*$</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Sanction</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>(?i)^\s*REACTIVATION_COMPTE\s*$</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Réactivation de compte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>(?i)^\s*CONTROLE_QUALITE\s*$</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>(?i)^\s*SYNTHESE_FLUX\s*$</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Synthèse des flux</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>(?i)^\s*FRACTIONNEMENT\s*$</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Fractionnement</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>(?i)^\s*COUVERTURE\s*$</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Couverture</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>(?i)^\s*GROS_MOUVEMENT_AGREGE\s*$</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Mouvement</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>(?i)^\s*a[_\s-]*revoir\s*$</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>À revoir</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Statut_revue</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>(?i)^\s*traitee?(?:_selon_regle_provisoire)?\s*$</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Traitée</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Statut_revue</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>(?i)^\s*couvert\s*$</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Couvert</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Statut_couverture</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>(?i)^\s*partiel\s*$</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Statut_couverture</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>(?i)^\s*non[_\s-]*couvert\s*$</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Non couvert</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Statut_couverture</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>(?i)^\s*non[_\s-]*automatisable\s*$</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Non automatisable</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Statut_couverture</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>(?i)^\s*elevee?\s*$</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Élevée</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Severite</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>(?i)^\s*38\ \-\ Synthese\ historique\ LBC\-FT\s*$</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>38 - Synthèse historique LBC-FT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>(?i)^\s*39\ \-\ Fractionnement\ potentiel\s*$</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>39 - Fractionnement potentiel</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>(?i)^\s*48\ \-\ Couverture\ du\ dispositif\ LBC\-FT\s*$</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>48 - Couverture du dispositif LBC-FT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>(?i)^\s*57\ \-\ Gros\ mouvements\ par\ periode\s*$</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>57 - Gros mouvements par période</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149\ \-\ Reporting\ LBC\-FT\s*$</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>149 - Reporting LBC-FT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149\ \-\ Detail\ des\ mouvements\ du\ reporting\s*$</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>149 - Détail des mouvements du reporting</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>(?i)^\s*149\ \-\ Remboursements\ anticipes\s*$</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>149 - Remboursements anticipés</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>(?i)^\s*150\ \-\ Alertes\ LBC\-FT\s*$</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>150 - Alertes LBC-FT</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>(?i)^\s*151\ \-\ Declarations\ de\ soupcon\ CENTIF\s*$</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>151 - Déclarations de soupçon CENTIF</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>(?i)^\s*152\ \-\ Profils\ de\ risque\ clients\s*$</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>152 - Profils de risque clients</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>(?i)^\s*153\ \-\ Referentiel\ sanctions\s*$</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>153 - Référentiel sanctions</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>(?i)^\s*154\ \-\ Comptes\ dormants\ reactives\s*$</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>154 - Comptes dormants réactivés</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>(?i)^\s*155\ \-\ Qualite\ des\ donnees\ LBC\-FT\s*$</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>155 - Qualité des données LBC-FT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Analyse_conformite</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Reporting\ agrege\s*$</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Reporting agrégé</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Mouvement\s*$</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mouvement</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Remboursement\ anticipe\s*$</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Remboursement anticipé</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Alerte\s*$</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Alerte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Declaration\s*$</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Déclaration</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Profil\ de\ risque\s*$</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Profil de risque</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Sanction\s*$</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sanction</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Reactivation\ de\ compte\s*$</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Réactivation de compte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Controle\ qualite\s*$</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Synthese\ des\ flux\s*$</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Synthèse des flux</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Fractionnement\s*$</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Fractionnement</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Couverture\s*$</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Couverture</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>(?i)^\s*Gros\ mouvement\ agrege\s*$</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Mouvement</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Type_element_conformite</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VRAI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
